--- a/naver-place-crawler/results_nail/대전_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/대전_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미공간 둔산점</t>
+          <t>둔산동 네일온</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mi_gonggan_@naver.com</t>
+          <t>nailon0224_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1386-7759</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 둔지로 11 트라이얼스타 B동 3층 305호</t>
+          <t>대전 서구 대덕대로 193 하나빌딩 2층 네일온</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mi_gonggan_</t>
+          <t>https://www.instagram.com/nailon_nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eajp</t>
+          <t>https://talk.naver.com/ct/w47rwv</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>714</v>
+        <v>5699</v>
       </c>
       <c r="Q2" t="n">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="R2" t="n">
-        <v>995</v>
+        <v>5811</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1148367339</t>
+          <t>1391452598</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148367339</t>
+          <t>https://m.place.naver.com/place/1391452598</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,12 +662,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>후이네일 둔산점</t>
+          <t>미공간 둔산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>seorinx3@naver.com</t>
+          <t>mi_gonggan_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -671,12 +675,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 둔산북로 22 둔산라이프종합상가 2층 211호</t>
+          <t>대전 서구 둔지로 11 트라이얼스타 B동 3층 305호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huinail3</t>
+          <t>https://blog.naver.com/mi_gonggan_</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -691,15 +695,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eajp</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1804</v>
+        <v>714</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="R3" t="n">
-        <v>1848</v>
+        <v>995</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1766527461</t>
+          <t>1148367339</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766527461</t>
+          <t>https://m.place.naver.com/place/1148367339</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +756,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헤이글네일</t>
+          <t>후이네일 둔산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chsll27@naver.com</t>
+          <t>seorinx3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1364-2353</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 서구 도산로 361 씨엘리오스위첸 상가동 210호</t>
+          <t>대전 서구 둔산북로 22 둔산라이프종합상가 2층 211호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heigl_nail</t>
+          <t>https://www.instagram.com/huinail3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2103</v>
+        <v>1804</v>
       </c>
       <c r="Q4" t="n">
         <v>44</v>
       </c>
       <c r="R4" t="n">
-        <v>2147</v>
+        <v>1848</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1698614402</t>
+          <t>1766527461</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698614402</t>
+          <t>https://m.place.naver.com/place/1766527461</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>둔산동 네일온</t>
+          <t>헤이글네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nailon0224_@naver.com</t>
+          <t>chsll27@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1386-7759</t>
+          <t>0507-1364-2353</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 193 하나빌딩 2층 네일온</t>
+          <t>대전 서구 도산로 361 씨엘리오스위첸 상가동 210호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon_nail</t>
+          <t>https://www.instagram.com/heigl_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -884,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47rwv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5694</v>
+        <v>2106</v>
       </c>
       <c r="Q5" t="n">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="R5" t="n">
-        <v>5806</v>
+        <v>2150</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1391452598</t>
+          <t>1698614402</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391452598</t>
+          <t>https://m.place.naver.com/place/1698614402</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="Q6" t="n">
         <v>207</v>
       </c>
       <c r="R6" t="n">
-        <v>3130</v>
+        <v>3132</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 앤 네일맘</t>
+          <t>엔피케어 대전서구점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nailmom0130@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1406-1846</t>
+          <t>0507-1453-7661</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 유성구 온천로 45 푸르지오시티 308호</t>
+          <t>대전 서구 대덕대로 164 2층 오렌지나무의원내 NP케어대전서구점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailmom0130</t>
+          <t>https://www.youtube.com/@NPCARE_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,17 +1080,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc3o6n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>292</v>
+        <v>140</v>
       </c>
       <c r="Q7" t="n">
-        <v>1042</v>
+        <v>114</v>
       </c>
       <c r="R7" t="n">
-        <v>1334</v>
+        <v>254</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>762256343</t>
+          <t>1172416189</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/762256343</t>
+          <t>https://m.place.naver.com/place/1172416189</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레푸스대전둔산점</t>
+          <t>레푸스 앤 네일맘</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>prettynail99@naver.com</t>
+          <t>nailmom0130@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1327-9918</t>
+          <t>0507-1406-1846</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 서구 둔산중로134번길 29 청사프라자 3층</t>
+          <t>대전 유성구 온천로 45 푸르지오시티 308호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/prettynail99</t>
+          <t>https://blog.naver.com/nailmom0130</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,12 +1179,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t0mq</t>
+          <t>https://talk.naver.com/ct/wc3o6n</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1197,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>447</v>
+        <v>292</v>
       </c>
       <c r="Q8" t="n">
-        <v>434</v>
+        <v>1042</v>
       </c>
       <c r="R8" t="n">
-        <v>881</v>
+        <v>1334</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20796051</t>
+          <t>762256343</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20796051</t>
+          <t>https://m.place.naver.com/place/762256343</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1234,39 +1230,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>프레나뷰티 괴정점</t>
+          <t>설브네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ds5795@naver.com</t>
+          <t>gooogooo94@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1342-2399</t>
+          <t>0507-1354-5386</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 도산로349번길 66 1층</t>
+          <t>대전 유성구 계룡로123번길 30 . 4층일부 사용</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xgaxmHK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1281,12 +1277,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc3d23</t>
+          <t>https://talk.naver.com/ct/w9ybc4d</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>690</v>
+        <v>212</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>247</v>
       </c>
       <c r="R9" t="n">
-        <v>723</v>
+        <v>459</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1306,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1306796793</t>
+          <t>1170713663</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306796793</t>
+          <t>https://m.place.naver.com/place/1170713663</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1332,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라브니크 뷰티</t>
+          <t>스테디네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jione123@naver.com</t>
+          <t>nbbi_k@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1403-0480</t>
+          <t>0507-1389-4945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 616 대전오렌지타운 2층 212호</t>
+          <t>대전 서구 도산로341번길 37 버베나1층 102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txdWWG</t>
+          <t>https://link.inpock.co.kr/steadynail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,7 +1365,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1379,27 +1375,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hlv8</t>
+          <t>https://talk.naver.com/ct/w41yyx</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>332</v>
+        <v>235</v>
       </c>
       <c r="Q10" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="R10" t="n">
-        <v>572</v>
+        <v>259</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1404,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1750926850</t>
+          <t>1043183025</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750926850</t>
+          <t>https://m.place.naver.com/place/1043183025</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1430,34 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유데모닉네일</t>
+          <t>네일뮤트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tpgmlwjs@naver.com</t>
+          <t>seoyoniee22@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1371-6590</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 도솔로 403-1 101호</t>
+          <t>대전 동구 백룡로5번길 9 1층 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hxiPeK/chat</t>
+          <t>https://www.instagram.com/nail.__.mute?igsh=d2ZvbnczMnl0N2ht&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1472,14 +1464,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rltj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>O</t>
@@ -1491,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>631</v>
+        <v>190</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>652</v>
+        <v>190</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,15 +1494,395 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1682054958</t>
+          <t>2093153296</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682054958</t>
+          <t>https://m.place.naver.com/place/2093153296</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>포브네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>thesaranail@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1306-8695</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 중구 대종로521번길 19 정우빌 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ncQqX</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>43</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2023432414</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023432414</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>네일수이룸</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yhkochina@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1482-4013</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대전 서구 둔산로 15 향촌상가 2층 207호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_WjQIX</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2060306237</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2060306237</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>히즈네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jennyrubyjane_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1303-8261</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>대전 서구 도산로403번길 45 1층 히즈네일</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyeez_nail/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0aw23</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10</v>
+      </c>
+      <c r="R14" t="n">
+        <v>18</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2033243510</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2033243510</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>모아네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>solate218007@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1409-8768</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>대전 서구 복수중로 30 상가동 2층 204호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_mwPAX</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>24</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2059636286</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2059636286</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_nail/대전_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/대전_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailon_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5699</v>
+        <v>5705</v>
       </c>
       <c r="Q2" t="n">
         <v>112</v>
       </c>
       <c r="R2" t="n">
-        <v>5811</v>
+        <v>5817</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -722,10 +722,10 @@
         <v>714</v>
       </c>
       <c r="Q3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="R3" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>seorinx3@naver.com</t>
+          <t>29nail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huinail3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="Q5" t="n">
         <v>44</v>
       </c>
       <c r="R5" t="n">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2925</v>
+        <v>2931</v>
       </c>
       <c r="Q6" t="n">
         <v>207</v>
       </c>
       <c r="R6" t="n">
-        <v>3132</v>
+        <v>3138</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NPCARE_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailmom0130</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1230,39 +1230,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>설브네일</t>
+          <t>모아네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gooogooo94@naver.com</t>
+          <t>solate218007@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1354-5386</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로123번길 30 . 4층일부 사용</t>
+          <t>대전 서구 탄방로 50-29 102호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://모아네일.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1277,7 +1273,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9ybc4d</t>
+          <t>https://talk.naver.com/ct/w19pe57</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1287,17 +1283,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="Q9" t="n">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="R9" t="n">
-        <v>459</v>
+        <v>265</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1170713663</t>
+          <t>2068481481</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170713663</t>
+          <t>https://m.place.naver.com/place/2068481481</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1328,44 +1324,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스테디네일</t>
+          <t>설브네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nbbi_k@naver.com</t>
+          <t>hoobooball@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1389-4945</t>
+          <t>0507-1354-5386</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 도산로341번길 37 버베나1층 102호</t>
+          <t>대전 유성구 계룡로123번길 30 . 4층일부 사용</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/steadynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1375,7 +1371,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41yyx</t>
+          <t>https://talk.naver.com/ct/w9ybc4d</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="R10" t="n">
-        <v>259</v>
+        <v>459</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,17 +1400,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1043183025</t>
+          <t>1170713663</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043183025</t>
+          <t>https://m.place.naver.com/place/1170713663</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1440,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.__.mute?igsh=d2ZvbnczMnl0N2ht&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,7 +1450,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1504,7 +1500,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1538,17 +1534,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ncQqX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1598,7 +1594,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1611,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>yhkochina@naver.com</t>
+          <t>lynnyy@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1632,17 +1628,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WjQIX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1786,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1824,17 +1820,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mwPAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1884,7 +1880,387 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>고요네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jurrr0068@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1310-8324</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>대전 서구 갈마역로25번길 17-8 1층 102호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>23</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2096979376</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2096979376</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네일도넛</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ksjksj7775@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1412-4465</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>대전 유성구 문화원로 106 2층 209호 유성캠퍼스타워</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0rwcko</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>51</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2022315496</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2022315496</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>네일더뮤즈</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>doyxniii@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1303-6533</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>대전 서구 구봉산북로7번길 70-14 1층 101호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>40</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2021738032</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021738032</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>유안테라피</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oironail@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1464-1737</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>대전 서구 도솔로335번길 4 101호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>29</v>
+      </c>
+      <c r="R19" t="n">
+        <v>35</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2008076870</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2008076870</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
